--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>11/10 13:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>325.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>325</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>10/10 02:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>12/10 14:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>200</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>10/10 02:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>200</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>10/10 02:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>12/10 16:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>175</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>175</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>10/10 16:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>175</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>12/10 15:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>150</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>12/10 15:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>10/10 17:15</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>150</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>150</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>10/10 16:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>150</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>150</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>150</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>10/10 17:15</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>140</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>10/10 15:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>150</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>150</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>150</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>12/10 19:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>95.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>95</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45940.06904672758</v>
+        <v>45940.06904672454</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,336 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>140</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+95,9%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45940.06904672454</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HK Poprad </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HK Poprad – HKM AS ZvolenExtraliga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+153%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45940.12636753461</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Presov </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HC Presov – NitraExtraliga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+153%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45940.12636753461</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dukla Mich</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Dukla Michalovce – Slovan BratislavaExtraliga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>12/10 14:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+144%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45940.12636753461</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kloten Fly</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kloten Flyers – DavosSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>11/10 17:45</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+95,9%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45940.12636753461</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Iserlohn –</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Iserlohn – Dresdner EislowenDEL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1,40%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+95,9%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45940.06904672758</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+94,6%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45940.12636753461</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Färjestad </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Färjestad BK – Örebro HKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>11/10 16:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+92,7%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45940.12636753461</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ilves Tamp</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ilves Tampere – HIFKFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10/10 15:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+90,3%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45940.12636753461</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>175</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45940.12636753461</v>
+        <v>45940.12636753472</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>175</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45940.12636753461</v>
+        <v>45940.12636753472</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>12/10 14:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>175</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45940.12636753461</v>
+        <v>45940.12636753472</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>11/10 17:45</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>125</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45940.12636753461</v>
+        <v>45940.12636753472</v>
       </c>
     </row>
     <row r="31">
@@ -1760,10 +1752,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>140</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1776,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45940.12636753461</v>
+        <v>45940.12636753472</v>
       </c>
     </row>
     <row r="32">
@@ -1805,10 +1795,8 @@
           <t>11/10 16:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>140</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1821,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45940.12636753461</v>
+        <v>45940.12636753472</v>
       </c>
     </row>
     <row r="33">
@@ -1850,10 +1838,8 @@
           <t>10/10 15:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>140</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1866,7 +1852,52 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45940.12636753461</v>
+        <v>45940.12636753472</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Kloten</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EHC Kloten – HC DavosNational League A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>11/10 17:45</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+95,1%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45940.18442289848</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,23 +1881,246 @@
           <t>11/10 17:45</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>125</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+95,1%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45940.18442289352</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Augsburger</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Augsburger Panther – Wolfsburg GrizzlyAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+167%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45940.22270311175</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ambri Piot</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ambri Piotta – AjoieSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+161%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45940.22270311175</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Fehervar A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fehervar AV19 – Pioneers VorarlbergAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>11/10 15:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+111%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45940.22270311175</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kosice – T</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Kosice – TrencinSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>12/10 13:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>+95,1%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>45940.18442289848</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+93,8%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45940.22270311175</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Spisska No</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Spisska Nova Ves – ZilinaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>12/10 14:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+93,4%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45940.22270311175</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>200</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45940.22270311175</v>
+        <v>45940.22270311342</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>175</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45940.22270311175</v>
+        <v>45940.22270311342</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>11/10 15:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>140</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45940.22270311175</v>
+        <v>45940.22270311342</v>
       </c>
     </row>
     <row r="38">
@@ -2059,10 +2053,8 @@
           <t>12/10 13:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>125</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2075,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45940.22270311175</v>
+        <v>45940.22270311342</v>
       </c>
     </row>
     <row r="39">
@@ -2104,10 +2096,8 @@
           <t>12/10 14:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>125</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2120,7 +2110,97 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45940.22270311175</v>
+        <v>45940.22270311342</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HKM AS Zvo</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HKM AS Zvolen – HC PresovExtraliga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>12/10 16:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+136%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45940.27247919689</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | RB Salzbou</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RB Salzbourg – Spusu Vienna CapitalsICE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10/10 17:15</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45940.27247919689</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,10 +2139,8 @@
           <t>12/10 16:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>175</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2155,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45940.27247919689</v>
+        <v>45940.27247920139</v>
       </c>
     </row>
     <row r="41">
@@ -2184,23 +2182,156 @@
           <t>10/10 17:15</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>140</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45940.27247920139</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zug – Genè</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Zug – Genève-ServetteSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45940.30598164468</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Black Wings LinzICE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10/10 17:15</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>1,50%</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>+110%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>45940.27247919689</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+112%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45940.30598164468</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Skelleftea</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Skelleftea AIK – HV 71SHL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>11/10 16:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+85,6%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45940.30598164468</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>150</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45940.30598164468</v>
+        <v>45940.30598164352</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>10/10 17:15</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>140</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45940.30598164468</v>
+        <v>45940.30598164352</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>11/10 16:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>125</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,97 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45940.30598164468</v>
+        <v>45940.30598164352</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EC Villach</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EC Villacher SV – HC Twk Innsbruck Die HaieICE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>11/10 13:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+174%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45940.35369755634</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.51re équipe | Zimbabwe –</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Zimbabwe – Afrique du Sud385076e7 International - Qualif. Afrique CDM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+89,9%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45940.35369755634</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>11/10 13:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>200</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45940.35369755634</v>
+        <v>45940.35369755787</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>90</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,52 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45940.35369755634</v>
+        <v>45940.35369755787</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Nitra – Ba</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Nitra – Banska BystricaExtraliga</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>12/10 15:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45940.3911716459</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -2440,10 +2440,8 @@
           <t>12/10 15:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>150</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45940.3911716459</v>
+        <v>45940.39117164352</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +2457,96 @@
         <v>45940.39117164352</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lukko Raum</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Lukko Rauma – JYP JyvaskylaLiiga</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>10/10 15:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45940.47113189623</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Rapperswil</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Rapperswil Jona Lakers – ZSC LionsSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+86,4%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45940.47113189623</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>10/10 15:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>140</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45940.47113189623</v>
+        <v>45940.47113189815</v>
       </c>
     </row>
     <row r="49">
@@ -2528,23 +2526,156 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>125</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+86,4%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45940.47113189815</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | MM Graz 99</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MM Graz 99ers – FTC-TelekomICE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>10/10 16:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+118%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45940.53001994292</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mountfield HK – PardubiceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>12/10 15:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+109%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45940.53001994292</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Litvinov –</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Litvinov – Kometa BrnoRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>12/10 15:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>+86,4%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>45940.47113189623</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+98,0%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45940.53001994292</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>10/10 16:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>150</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45940.53001994292</v>
+        <v>45940.53001994213</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>12/10 15:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>140</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45940.53001994292</v>
+        <v>45940.53001994213</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>12/10 15:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>125</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,142 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45940.53001994292</v>
+        <v>45940.53001994213</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Argentine </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Argentine – VenezuelaMatchs amicaux internationaux</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>11/10 00:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+184%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45940.56277157716</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Lausanne – EHC BielNational League A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+120%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45940.56277157716</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Mountfield HK – HC PardubiceExtraliga</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>12/10 15:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+103%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45940.56277157716</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -2698,10 +2698,8 @@
           <t>11/10 00:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>200</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45940.56277157716</v>
+        <v>45940.56277157408</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>150</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45940.56277157716</v>
+        <v>45940.56277157408</v>
       </c>
     </row>
     <row r="55">
@@ -2788,10 +2784,8 @@
           <t>12/10 15:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>140</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2804,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45940.56277157716</v>
+        <v>45940.56277157408</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,6 +2801,321 @@
         <v>45940.56277157408</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Tampa Bay </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tampa Bay Lightning – New Jersey DevilsNHL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>11/10 23:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+150%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45940.63959301206</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Detroit Re</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Detroit Red Wings – Toronto Maple LeafsNHL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>11/10 23:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+147%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45940.63959301206</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Carolina H</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Carolina Hurricanes – Philadelphia FlyersNHL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>11/10 23:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+144%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45940.63959301206</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Boston Bru</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Boston Bruins – Buffalo SabresNHL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>11/10 23:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+143%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45940.63959301206</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Minnesota </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Minnesota Wild – Columbus Blue JacketsNHL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>12/10 00:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+131%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45940.63959301206</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.51re équipe | Zimbabwe –</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Zimbabwe – Afrique du SudCDM - Qualifs Afrique</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+118%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45940.63959301206</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Florida Pa</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Florida Panthers – Ottawa Senators385076e7 NHL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>11/10 23:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+117%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45940.63959301206</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>11/10 23:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>200</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45940.63959301206</v>
+        <v>45940.63959300926</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>11/10 23:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>200</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45940.63959301206</v>
+        <v>45940.63959300926</v>
       </c>
     </row>
     <row r="58">
@@ -2917,10 +2913,8 @@
           <t>11/10 23:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>200</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2933,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45940.63959301206</v>
+        <v>45940.63959300926</v>
       </c>
     </row>
     <row r="59">
@@ -2962,10 +2956,8 @@
           <t>11/10 23:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>200</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2978,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45940.63959301206</v>
+        <v>45940.63959300926</v>
       </c>
     </row>
     <row r="60">
@@ -3007,10 +2999,8 @@
           <t>12/10 00:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>175</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3023,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45940.63959301206</v>
+        <v>45940.63959300926</v>
       </c>
     </row>
     <row r="61">
@@ -3052,10 +3042,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>110</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3068,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45940.63959301206</v>
+        <v>45940.63959300926</v>
       </c>
     </row>
     <row r="62">
@@ -3097,23 +3085,336 @@
           <t>11/10 23:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>175</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+117%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45940.63959300926</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Löwen Fran</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Löwen Frankfurt – Eisbären BerlinAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+168%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45940.68534522627</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Chicago Bl</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Chicago Blackhawks – Montreal CanadiensNHL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>11/10 23:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+167%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45940.68534522627</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Colorado A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Colorado Avalanche – Dallas StarsNHL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>12/10 01:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+167%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45940.68534522627</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Edmonton O</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Edmonton Oilers – Vancouver CanucksNHL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>12/10 02:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+161%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45940.68534522627</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Pittsburgh</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Pittsburgh Penguins – NY RangersNHL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>11/10 23:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>+117%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>45940.63959301206</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+131%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45940.68534522627</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Nashville </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Nashville Predators – Utah Hockey ClubNHL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>12/10 00:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+130%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45940.68534522627</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Calgary Fl</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Calgary Flames – St. Louis BluesNHL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>11/10 20:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+130%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45940.68534522627</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>200</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45940.68534522627</v>
+        <v>45940.68534523148</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>11/10 23:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>200</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45940.68534522627</v>
+        <v>45940.68534523148</v>
       </c>
     </row>
     <row r="65">
@@ -3218,10 +3214,8 @@
           <t>12/10 01:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>200</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3234,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45940.68534522627</v>
+        <v>45940.68534523148</v>
       </c>
     </row>
     <row r="66">
@@ -3263,10 +3257,8 @@
           <t>12/10 02:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>200</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3279,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45940.68534522627</v>
+        <v>45940.68534523148</v>
       </c>
     </row>
     <row r="67">
@@ -3308,10 +3300,8 @@
           <t>11/10 23:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>175</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3324,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45940.68534522627</v>
+        <v>45940.68534523148</v>
       </c>
     </row>
     <row r="68">
@@ -3353,10 +3343,8 @@
           <t>12/10 00:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>175</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3369,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45940.68534522627</v>
+        <v>45940.68534523148</v>
       </c>
     </row>
     <row r="69">
@@ -3398,23 +3386,111 @@
           <t>11/10 20:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="n">
+        <v>175</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+130%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45940.68534523148</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KooKoo – J</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>KooKoo – JukuritFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>11/10 14:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>+130%</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>45940.68534522627</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+132%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45940.72119656646</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Straubing </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Straubing – Wild WingsDEL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+115%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45940.72119656646</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3429,10 +3429,8 @@
           <t>11/10 14:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>175</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3445,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45940.72119656646</v>
+        <v>45940.7211965625</v>
       </c>
     </row>
     <row r="71">
@@ -3474,23 +3472,156 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="n">
+        <v>150</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+115%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45940.7211965625</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Eisbären B</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Eisbären Berlin – Nurnberg Ice TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>12/10 12:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>225.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+184%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45940.77098968589</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | KAC – HC P</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>KAC – HC PustertalAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>12/10 15:30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>+115%</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>45940.72119656646</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+121%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45940.77098968589</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | New York I</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>New York Islanders – Washington CapitalsNHL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>11/10 23:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+101%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45940.77098968589</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3515,10 +3515,8 @@
           <t>12/10 12:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>225</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3531,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45940.77098968589</v>
+        <v>45940.7709896875</v>
       </c>
     </row>
     <row r="73">
@@ -3560,10 +3558,8 @@
           <t>12/10 15:30</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>150</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3576,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45940.77098968589</v>
+        <v>45940.7709896875</v>
       </c>
     </row>
     <row r="74">
@@ -3605,10 +3601,8 @@
           <t>11/10 23:00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>150</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3621,7 +3615,97 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45940.77098968589</v>
+        <v>45940.7709896875</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Berlin – N</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Berlin – Nuremberg Ice TigersDEL stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>12/10 12:00</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+158%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45940.80338908972</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Genève-Ser</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Genève-Servette – LausanneSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>12/10 12:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+155%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45940.80338908972</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -3644,10 +3644,8 @@
           <t>12/10 12:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>200</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3660,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45940.80338908972</v>
+        <v>45940.80338908565</v>
       </c>
     </row>
     <row r="76">
@@ -3689,10 +3687,8 @@
           <t>12/10 12:00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>175</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3705,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45940.80338908972</v>
+        <v>45940.80338908565</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3704,6 +3704,186 @@
         <v>45940.80338908565</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Genève-Ser</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Genève-Servette – LausanneNational League A</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>12/10 12:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+154%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45940.88782724603</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Mhk 32 Lip</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Mhk 32 Liptovsky Mikulas – HK PopradExtraliga</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>12/10 15:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+107%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45940.88782724603</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.52e équipe | Cap Vert –</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cap Vert – EswatiniInternational - Qualif. Afrique CDM</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>13/10 16:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>95.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+105%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45940.88782724603</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Langnau Ti</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Langnau Tigers – Rapperswil Jona LakersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>11/10 17:45</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+105%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45940.88782724603</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3730,10 +3730,8 @@
           <t>12/10 12:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>175</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3746,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45940.88782724603</v>
+        <v>45940.88782724537</v>
       </c>
     </row>
     <row r="78">
@@ -3775,10 +3773,8 @@
           <t>12/10 15:00</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>150</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3791,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45940.88782724603</v>
+        <v>45940.88782724537</v>
       </c>
     </row>
     <row r="79">
@@ -3820,10 +3816,8 @@
           <t>13/10 16:00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>95.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>95</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3836,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45940.88782724603</v>
+        <v>45940.88782724537</v>
       </c>
     </row>
     <row r="80">
@@ -3865,10 +3859,8 @@
           <t>11/10 17:45</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>150</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3881,7 +3873,97 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45940.88782724603</v>
+        <v>45940.88782724537</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | ERC Ingols</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ERC Ingolstadt – Lowen FrankfurtDEL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>12/10 14:30</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+117%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45940.93001954112</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Vienne Cap</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Vienne Capitals – Graz 99ersAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>12/10 14:30</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45940.93001954112</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-10.xlsx
+++ b/data/valuebets_database_2025-10-10.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3902,10 +3902,8 @@
           <t>12/10 14:30</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>175</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3918,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45940.93001954112</v>
+        <v>45940.93001953704</v>
       </c>
     </row>
     <row r="82">
@@ -3947,23 +3945,201 @@
           <t>12/10 14:30</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" t="n">
+        <v>140</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45940.93001953704</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ingolstadt</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ingolstadt – Löwen FrankfurtAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>12/10 14:30</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+138%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45940.97109410484</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kölner Hai</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Kölner Haie – Iserlohn RoostersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>12/10 17:00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45940.97109410484</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Grizzlys W</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Grizzlys Wolfsburg – StraubingDEL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>12/10 14:30</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+115%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45940.97109410484</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | EHC Biel-B</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EHC Biel-Bienne – Fribourg GotteronSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>11/10 17:45</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>140.00</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>+113%</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>45940.93001954112</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+115%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45940.97109410484</v>
       </c>
     </row>
   </sheetData>
